--- a/artfynd/A 5148-2026 artfynd.xlsx
+++ b/artfynd/A 5148-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5054007</v>
+        <v>2433623</v>
       </c>
       <c r="B2" t="n">
-        <v>98519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>220075</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Håckbergets östsluttning, Vrm</t>
+          <t>Håckberget strax O, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>421451.4899265806</v>
+        <v>421543</v>
       </c>
       <c r="R2" t="n">
-        <v>6611946.58737113</v>
+        <v>6612010</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,21 +743,11 @@
           <t>2010-06-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2010-06-09</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,7 +759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Ängsgranskog</t>
+          <t>Fuktig granskogsglänta</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5281329</v>
+        <v>3424189</v>
       </c>
       <c r="B3" t="n">
-        <v>98430</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,37 +788,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Håckbergets östsluttning, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>421488.2641623132</v>
+        <v>421451</v>
       </c>
       <c r="R3" t="n">
-        <v>6611984.762169327</v>
+        <v>6611947</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,19 +850,9 @@
           <t>2010-06-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2010-06-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3424189</v>
+        <v>4222297</v>
       </c>
       <c r="B4" t="n">
-        <v>103264</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,42 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Håckbergets östsluttning, Vrm</t>
+          <t>Håckberget strax O, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>421451.4899265806</v>
+        <v>421563</v>
       </c>
       <c r="R4" t="n">
-        <v>6611946.58737113</v>
+        <v>6612038</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,21 +952,11 @@
           <t>2010-06-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2010-06-09</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1013,7 +968,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Ängsgranskog</t>
+          <t>Bäckravin</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1031,15 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4222297</v>
+        <v>5054007</v>
       </c>
       <c r="B5" t="n">
-        <v>95518</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,37 +997,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Håckberget strax O, Vrm</t>
+          <t>Håckbergets östsluttning, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>421563.3487868283</v>
+        <v>421451</v>
       </c>
       <c r="R5" t="n">
-        <v>6612037.813312807</v>
+        <v>6611947</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,21 +1054,11 @@
           <t>2010-06-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2010-06-09</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1130,7 +1070,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Bäckravin</t>
+          <t>Ängsgranskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1145,6 +1085,108 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5281329</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Håckbergets östsluttning, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>421488</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6611985</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nyed</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2010-06-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2010-06-09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Ängsgranskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Crister Albinsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Crister Albinsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5148-2026 artfynd.xlsx
+++ b/artfynd/A 5148-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2433623</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3424189</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4222297</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5054007</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,8 +1212,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5281329</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>